--- a/docs/01_요구사항정의서.xlsx
+++ b/docs/01_요구사항정의서.xlsx
@@ -101,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -159,6 +203,8 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -552,6 +598,9 @@
           <t>요구사항정의서 (사용자 관점)</t>
         </is>
       </c>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -561,9 +610,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -576,6 +628,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -588,6 +643,9 @@
           <t>✅ 완료 / 🔧 진행중 / ⬜ 예정</t>
         </is>
       </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="12" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -860,243 +918,297 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CL-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>사진을 찍으면 AI가 옷 종류·색을 인식해 등록을 도와야 한다(여러 장 동시, 확인 후 저장)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>등록 편의 — 입력 3필드를 사진 한 장으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>REQ-FAV-01</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>마음에 든 코디를 찜하고 다시 볼 수 있어야 한다</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>재방문</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>REQ-SET-01</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>성별·피부톤·사이즈·핏·선호 아이템을 설정할 수 있어야 한다</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>추천 개인화</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>REQ-AUTH-01</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>이메일/비밀번호로 가입·로그인하고, 로그인해야 앱을 쓸 수 있어야 한다</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>회원제·접근 제한</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>REQ-AUTH-02</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>회원가입 시 비밀번호 확인·이름을 입력해야 한다</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>오타 방지·식별</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>REQ-AUTH-03</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>가입 시 이메일 인증을 거쳐야 로그인할 수 있어야 한다</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>가짜 이메일 방지·신뢰</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>REQ-AUTH-04</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>비밀번호를 잊었을 때 재설정할 수 있어야 한다</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>계정 복구(상용 필수)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>REQ-SYNC-01</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>옷장·찜·설정이 계정에 저장돼 다른 기기서도 동기화돼야 한다</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>기기 간 동기화</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>REQ-PERF-01</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>같은 조건의 추천은 빠르게(재호출 없이) 떠야 한다</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>로딩 시간 단축</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PERF-02</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>새 조건의 추천도 첫 코디가 빨리 보여야 한다</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>첫 로딩 체감 단축(~10초→~3초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>REQ-DEPLOY-01</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>외부(휴대폰)에서 접속 가능하도록 배포돼야 한다</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
@@ -1121,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1170,6 +1282,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CL-03(사진 옷 등록)·REQ-PERF-02(첫 추천 1세트 우선) 추가, REQ-AUTH-04 완료 반영(누락 갱신)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/01_요구사항정의서.xlsx
+++ b/docs/01_요구사항정의서.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>가입 시 이메일 인증을 거쳐야 로그인할 수 있어야 한다</t>
+          <t>가입 시 이메일 인증(인증코드)을 완료해야 가입할 수 있어야 한다</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1299,6 +1299,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-03 갱신 — 가입 후 링크 인증에서 가입 전 인증코드 확인으로</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
